--- a/output/pdf_financials_xlsx/RIWI.xlsx
+++ b/output/pdf_financials_xlsx/RIWI.xlsx
@@ -3447,25 +3447,25 @@
         <v>0.026354</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.059786</v>
+        <v>0.034786</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.047657</v>
+        <v>0.027729</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.63679</v>
+        <v>0.056283</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.819777</v>
+        <v>0.057494</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.525539</v>
+        <v>0.088084</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.387003</v>
+        <v>0.226224</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.155041</v>
+        <v>0.09057800000000001</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>0.178701</v>
@@ -6195,10 +6195,8 @@
       <c r="C107" s="3" t="n">
         <v>0.567673</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0.953048</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.759703</v>
@@ -12275,7 +12273,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -14687,7 +14685,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -16845,7 +16843,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RIWI.xlsx
+++ b/output/pdf_financials_xlsx/RIWI.xlsx
@@ -534,22 +534,30 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0.007990000000000001</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.001929</v>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0.002405</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.023661</v>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
@@ -566,17 +574,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>0.038195</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.092942</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.07119499999999999</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0.003667</v>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -635,11 +651,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>-0.019596</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-0.172497</v>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1171,28 +1191,28 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0</v>
+        <v>1.14575</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>1.525041</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>2.582879</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>2.094734</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0</v>
+        <v>2.274802</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>2.417694</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>3.666403</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>4.758252</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>4.517947</v>
@@ -1214,28 +1234,28 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.343844</v>
+        <v>-0.801906</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.755765</v>
+        <v>-0.769276</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.808524</v>
+        <v>-1.774355</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.346057</v>
+        <v>-0.748677</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2.667677</v>
+        <v>0.392875</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3.110878</v>
+        <v>0.693184</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4.580738</v>
+        <v>0.914335</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.135701</v>
+        <v>-0.622551</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-1.730567</v>
@@ -1257,19 +1277,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>0.007990000000000001</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>0.001929</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>0.002405</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>0.023661</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0</v>
@@ -1281,16 +1301,16 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>0.038195</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>0.092942</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0</v>
+        <v>0.07119499999999999</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0</v>
+        <v>0.003667</v>
       </c>
     </row>
     <row r="19">
@@ -1954,16 +1974,16 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-0.793916</v>
+        <v>-0.801906</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-0.850488</v>
+        <v>-0.852417</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>-1.774355</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-0.746272</v>
+        <v>-0.748677</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0.392875</v>
@@ -1978,16 +1998,16 @@
         <v>-0.627149</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>-1.692372</v>
+        <v>-1.730567</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-0.83575</v>
+        <v>-0.928692</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>-0.725673</v>
+        <v>-0.796868</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>-2.444462</v>
+        <v>-2.448129</v>
       </c>
     </row>
     <row r="34">
@@ -2040,16 +2060,16 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-0.792762</v>
+        <v>-0.800752</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-0.848954</v>
+        <v>-0.8508829999999999</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>-1.773023</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.741506</v>
+        <v>-0.743911</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0.409232</v>
@@ -2064,16 +2084,16 @@
         <v>-0.627149</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-1.692372</v>
+        <v>-1.730567</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-0.83575</v>
+        <v>-0.928692</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.725673</v>
+        <v>-0.796868</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>-2.444462</v>
+        <v>-2.448129</v>
       </c>
     </row>
     <row r="36">
@@ -2083,16 +2103,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-230.558625423157</v>
+        <v>-232.8823536254813</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-112.330420170291</v>
+        <v>-112.585658240326</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>-219.2913259222979</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-55.08726599245054</v>
+        <v>-55.26593598933774</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>15.3403879105304</v>
@@ -2107,16 +2127,16 @@
         <v>-15.16427323928882</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-60.71551062287883</v>
+        <v>-62.08579382789573</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-19.97071837475749</v>
+        <v>-22.19161996875894</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-14.12337795036218</v>
+        <v>-15.50900741869851</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-43.09546803869114</v>
+        <v>-43.16011665310932</v>
       </c>
     </row>
     <row r="37">
@@ -3447,25 +3467,25 @@
         <v>0.026354</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.034786</v>
+        <v>0.059786</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.027729</v>
+        <v>0.047657</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.056283</v>
+        <v>0.63679</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.057494</v>
+        <v>0.819777</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.088084</v>
+        <v>0.525539</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.226224</v>
+        <v>0.387003</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.09057800000000001</v>
+        <v>0.155041</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>0.178701</v>
@@ -7597,19 +7617,19 @@
         <v>0</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>0</v>
+        <v>-0.041568</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>0</v>
+        <v>-0.052578</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>0</v>
+        <v>-0.052733</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>0</v>
+        <v>-0.049778</v>
       </c>
       <c r="K139" s="3" t="n">
-        <v>0</v>
+        <v>-0.017305</v>
       </c>
       <c r="L139" s="3" t="n">
         <v>0</v>
@@ -7640,19 +7660,19 @@
         <v>0</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>0</v>
+        <v>-0.041568</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>0</v>
+        <v>-0.052578</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>0</v>
+        <v>-0.052733</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>0</v>
+        <v>-0.049778</v>
       </c>
       <c r="K140" s="3" t="n">
-        <v>0</v>
+        <v>-0.017305</v>
       </c>
       <c r="L140" s="3" t="n">
         <v>0</v>
@@ -12273,7 +12293,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -14685,7 +14705,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -16303,7 +16323,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -20395,7 +20415,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -23759,7 +23783,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -29001,7 +29029,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -29077,7 +29105,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -30897,7 +30925,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -31809,7 +31837,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E317" s="5" t="n">
@@ -33893,7 +33921,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -33971,7 +33999,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E346" s="5" t="n">
@@ -34279,7 +34307,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">

--- a/output/pdf_financials_xlsx/RIWI.xlsx
+++ b/output/pdf_financials_xlsx/RIWI.xlsx
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.001154</v>
+        <v>0.003127</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.001534</v>
+        <v>0.006139</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.001332</v>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-0.800752</v>
+        <v>-0.798779</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-0.8508829999999999</v>
+        <v>-0.846278</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>-1.773023</v>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-232.8823536254813</v>
+        <v>-232.3085468991752</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-112.585658240326</v>
+        <v>-111.9763418522953</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>-219.2913259222979</v>
@@ -6568,19 +6568,19 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.003127</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.006139</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.001332</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.004766</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.016357</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -19189,7 +19189,11 @@
           <t>Additions of intangible assets</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -24839,7 +24843,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
@@ -26205,7 +26209,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27209,7 +27217,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E256" s="5" t="n">
         <v>0.001973</v>
       </c>

--- a/output/pdf_financials_xlsx/RIWI.xlsx
+++ b/output/pdf_financials_xlsx/RIWI.xlsx
@@ -1513,10 +1513,10 @@
         <v>-0.270581</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.08658100000000001</v>
+        <v>-0.08658100000000001</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.001163</v>
+        <v>-0.001163</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0.022409</v>
@@ -4768,30 +4768,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" s="3" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0.043909</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0.046886</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0.049778</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.022024</v>
       </c>
       <c r="K82" s="1" t="inlineStr">
         <is>
@@ -4835,30 +4825,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F83" s="3" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.043909</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.046886</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.049778</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.022024</v>
       </c>
       <c r="K83" s="1" t="inlineStr">
         <is>
@@ -5054,19 +5034,19 @@
         <v>0</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.00291</v>
+        <v>0</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.043909</v>
+        <v>0</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.14175</v>
+        <v>0.094864</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.049778</v>
+        <v>0</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.022024</v>
+        <v>0</v>
       </c>
       <c r="K87" s="3" t="n">
         <v>0</v>
@@ -5350,30 +5330,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" s="3" t="n">
+        <v>0.001187734256092648</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.01078594773449408</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.009548511759173687</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0.01086869421737345</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.006995783598279896</v>
       </c>
       <c r="K92" s="1" t="inlineStr">
         <is>
@@ -6706,7 +6676,7 @@
         <v>-0.008432</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.035858</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -6835,7 +6805,7 @@
         <v>-0.0251</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0.338113</v>
+        <v>0.302255</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0.024892</v>
@@ -6878,31 +6848,31 @@
         <v>0.377525</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0</v>
+        <v>0.323913</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0</v>
+        <v>0.416269</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>0</v>
+        <v>0.545117</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0</v>
+        <v>0.09249599999999999</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0</v>
+        <v>0.259448</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>0</v>
+        <v>0.355206</v>
       </c>
       <c r="L122" s="3" t="n">
-        <v>0</v>
+        <v>0.157088</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>0</v>
+        <v>0.193934</v>
       </c>
     </row>
     <row r="123">
@@ -7256,7 +7226,7 @@
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>0</v>
+        <v>-0.00396</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -7265,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0</v>
+        <v>-0.08081000000000001</v>
       </c>
       <c r="F131" s="3" t="n">
         <v>0</v>
@@ -7399,10 +7369,8 @@
       <c r="F134" s="3" t="n">
         <v>-0.032171</v>
       </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G134" s="3" t="n">
+        <v>0.027249</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0.016439</v>
@@ -7855,7 +7823,7 @@
         <v>1.29183</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>0</v>
+        <v>0.002405</v>
       </c>
       <c r="G144" s="3" t="n">
         <v>0.124401</v>
@@ -7885,10 +7853,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B145" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B145" s="3" t="n">
+        <v>1.422384</v>
       </c>
       <c r="C145" s="3" t="n">
         <v>0.814347</v>
@@ -8016,10 +7982,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B148" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B148" s="3" t="n">
+        <v>0.814347</v>
       </c>
       <c r="C148" s="3" t="n">
         <v>0.210063</v>
@@ -8119,18 +8083,16 @@
         <v>-0.10881</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>0.283088</v>
-      </c>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.280683</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>1.147021</v>
       </c>
       <c r="H150" s="3" t="n">
         <v>0.9570109999999999</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>0.260241</v>
+        <v>0.258993</v>
       </c>
       <c r="J150" s="3" t="n">
         <v>-1.478009</v>
@@ -11551,7 +11513,11 @@
           <t>Current portion of lease obligations</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -12673,7 +12639,11 @@
           <t>Current portion of lease obligations (Note 10)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -13579,7 +13549,11 @@
           <t>Current portion of lease obligations (Note 9)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -18331,7 +18305,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -18479,7 +18457,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -21619,7 +21601,11 @@
           <t>Share-based payment expense (Note 9, 12) 259,448</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -23425,7 +23411,11 @@
           <t>Share-based payment expense (Note 8)</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -23569,7 +23559,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -24243,7 +24237,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -24989,7 +24987,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -25523,7 +25525,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -27521,7 +27527,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E260" s="5" t="n">
         <v>-0.00396</v>
       </c>
@@ -28067,7 +28077,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
         <v>1.422384</v>
       </c>
@@ -28141,7 +28155,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E268" s="5" t="n">
         <v>0.814347</v>
       </c>
@@ -31399,7 +31417,11 @@
           <t>Income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -32133,7 +32155,11 @@
           <t>Income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -32875,7 +32901,11 @@
           <t>Income tax (recovery) expense (Note 12)</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
